--- a/testat-english-vocabulary/English_Lesson_Template.xlsx
+++ b/testat-english-vocabulary/English_Lesson_Template.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="9XE4ROgUgyySOy2GkIj1HL21X81uWRtVs1dZn3ZI1ICH2s6N3w4DqM7fX85RU2mmoAzikRRdpLBKpwH7rlnbrg==" workbookSaltValue="c8VjlukAebPaSOZB0Fl8zw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView windowHeight="18285" firstSheet="3"/>
   </bookViews>
@@ -72,7 +73,7 @@
     <t>TYPE:STANDARD</t>
   </si>
   <si>
-    <t>الترجمة العربية</t>
+    <t>الكلمة العربية</t>
   </si>
   <si>
     <t>الكلمة الإنجليزية</t>
@@ -90,7 +91,7 @@
     <t>TITLE_AR:الكلمات الإضافية</t>
   </si>
   <si>
-    <t>المعنى العربي</t>
+    <t>التعبير العربي</t>
   </si>
   <si>
     <t>التعبير الإنجليزي</t>
@@ -103,9 +104,6 @@
   </si>
   <si>
     <t>TYPE:DEFINITIONS</t>
-  </si>
-  <si>
-    <t>الكلمة العربية</t>
   </si>
   <si>
     <t>التعريف العربي</t>
@@ -148,6 +146,9 @@
   </si>
   <si>
     <t>TYPE:VERBS</t>
+  </si>
+  <si>
+    <t>المعنى العربي</t>
   </si>
   <si>
     <t>Past Participle (V3)</t>
@@ -950,7 +951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -969,6 +970,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -983,10 +987,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1083,10 +1087,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FF6600"/>
-      <color rgb="0038014E"/>
       <color rgb="00FF9B73"/>
       <color rgb="00F5F3F8"/>
+      <color rgb="0038014E"/>
+      <color rgb="00FF6600"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1388,67 +1392,67 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.5714285714286" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="74" customWidth="1"/>
-    <col min="3" max="3" width="77" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="115.857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" hidden="1" customHeight="1" spans="1:3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" ht="54" spans="1:3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="19"/>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" ht="54" spans="1:3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="19"/>
+      <c r="C4" s="20"/>
     </row>
     <row r="5" ht="54" spans="1:3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="19"/>
+      <c r="C5" s="20"/>
     </row>
     <row r="6" ht="54.75" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="23"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="94DFMMdmZVK6VwybaHtvsRT2l2APGFdQBBnD/WZBvWELeX7/FN3re5OjQsU/WHaXrZvuQK88TI/ea628EUh/fQ==" saltValue="7e/vYq/u9Ul/5cdDjkAtIw==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1eagjWMVdlMd8h4eb++s4wkUAIwOPeTgu9gv/bv7pttBiald5JOyipwKinyGcz3rG/4MlF82OCmO+PG2qEmhyQ==" saltValue="7SOcWOt5S9SmBlXcDlIxmw==" spinCount="100000" sheet="1" objects="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
@@ -1466,17 +1470,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="54" customWidth="1"/>
+    <col min="2" max="3" width="61.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5483,7 +5487,7 @@
       <c r="C1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="l9rq+6sF6sqTr5pKN9EggTjCgz+rHctXmNdYBMZxFpj+ci8vswr+NSZIf8vgPljbPrFSuoDFafnK5TXW3cKF4Q==" saltValue="H+NOVnEp06VEzxlhd2z0og==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eq3rtFmDxqdIhNPD77JWqJmYfEMGK8F9v/XnAZZ+CrNdofXTRkY1sI+f72+/cS4Kjj1fOKxkRt2drLWmrZxVKw==" saltValue="aV0mNJG9G2+FJdeCoFLgkg==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="B2:C312">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>"ISEVEN(ROW())"</formula>
@@ -5520,17 +5524,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="54" customWidth="1"/>
+    <col min="2" max="3" width="61.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9537,7 +9541,7 @@
       <c r="C1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="El7mhKb8QiFdfn3wrzJHYx+9fM/VOFWHZkEzeEvbUEYOtxqbk6NK3s6UjfhCmxRMZ+I/74DXHmh1+eN3Of4EtQ==" saltValue="+6heZCMZSNiL6smkDGk6ow==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EI64fiCnN79fifGrn+vNskF/nafY2FZz8t8CjqYU5ruhxXxXZ9AyNnQwS0AAdUjiveCMx1sV9plZg6x4V3Cung==" saltValue="ADqJwmtk/8aew5nLxqFsoA==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="B2:C312">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>"ISEVEN(ROW())"</formula>
@@ -9574,17 +9578,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="54" customWidth="1"/>
+    <col min="2" max="3" width="61.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9592,8 +9596,8 @@
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" ht="27" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -13592,7 +13596,7 @@
       <c r="C1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="znZheDMQyOr/SeuLI0KrZ8Nc69EW0NBWTwzSJZiNBjB+gLvTticXkPYkgZbzJSoE3mKPQue2blf6Qvpj0L7Rjw==" saltValue="L/YEXCz3A8d7ZptW/X9zug==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lLpI/Mrdc6fPEwgaki6jhMuvgzeA9s6qiMpDQazVlWYCtAU8WHEWOZTY6QhmHGjs72LfoIXAFei99etTLkHWng==" saltValue="iiljnclbACRkkgtjabq07A==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="B3:C153">
     <cfRule type="expression" dxfId="0" priority="10">
       <formula>ISEVEN(ROW())</formula>
@@ -13640,30 +13644,30 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="34.7142857142857" customWidth="1"/>
-    <col min="4" max="5" width="60.7142857142857" customWidth="1"/>
+    <col min="2" max="3" width="50.7142857142857" customWidth="1"/>
+    <col min="4" max="5" width="100.714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2" ht="27" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -13672,7 +13676,7 @@
     </row>
     <row r="3" ht="27" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -14581,688 +14585,688 @@
       <c r="E153" s="5"/>
     </row>
     <row r="154" ht="27" spans="2:5">
-      <c r="B154" s="7"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="8"/>
+      <c r="E154" s="8"/>
     </row>
     <row r="155" ht="27" spans="2:5">
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
     </row>
     <row r="156" ht="27" spans="2:5">
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
     </row>
     <row r="157" ht="27" spans="2:5">
-      <c r="B157" s="7"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="8"/>
+      <c r="E157" s="8"/>
     </row>
     <row r="158" ht="27" spans="2:5">
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="8"/>
+      <c r="E158" s="8"/>
     </row>
     <row r="159" ht="27" spans="2:5">
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="9"/>
+      <c r="E159" s="9"/>
     </row>
     <row r="160" ht="27" spans="2:5">
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="9"/>
+      <c r="E160" s="9"/>
     </row>
     <row r="161" ht="27" spans="2:5">
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="9"/>
     </row>
     <row r="162" ht="27" spans="2:5">
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
+      <c r="E162" s="9"/>
     </row>
     <row r="163" ht="27" spans="2:5">
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
+      <c r="E163" s="9"/>
     </row>
     <row r="164" ht="27" spans="2:5">
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
+      <c r="B164" s="9"/>
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
+      <c r="E164" s="9"/>
     </row>
     <row r="165" ht="27" spans="2:5">
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
     </row>
     <row r="166" ht="27" spans="2:5">
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
+      <c r="B166" s="9"/>
+      <c r="C166" s="9"/>
+      <c r="D166" s="9"/>
+      <c r="E166" s="9"/>
     </row>
     <row r="167" ht="27" spans="2:5">
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
+      <c r="B167" s="9"/>
+      <c r="C167" s="9"/>
+      <c r="D167" s="9"/>
+      <c r="E167" s="9"/>
     </row>
     <row r="168" ht="27" spans="2:5">
-      <c r="B168" s="8"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
+      <c r="E168" s="9"/>
     </row>
     <row r="169" ht="27" spans="2:5">
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
+      <c r="B169" s="9"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
     </row>
     <row r="170" ht="27" spans="2:5">
-      <c r="B170" s="8"/>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
+      <c r="B170" s="9"/>
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
+      <c r="E170" s="9"/>
     </row>
     <row r="171" ht="27" spans="2:5">
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="9"/>
     </row>
     <row r="172" ht="27" spans="2:5">
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
+      <c r="B172" s="9"/>
+      <c r="C172" s="9"/>
+      <c r="D172" s="9"/>
+      <c r="E172" s="9"/>
     </row>
     <row r="173" ht="27" spans="2:5">
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
+      <c r="B173" s="9"/>
+      <c r="C173" s="9"/>
+      <c r="D173" s="9"/>
+      <c r="E173" s="9"/>
     </row>
     <row r="174" ht="27" spans="2:5">
-      <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
+      <c r="B174" s="9"/>
+      <c r="C174" s="9"/>
+      <c r="D174" s="9"/>
+      <c r="E174" s="9"/>
     </row>
     <row r="175" ht="27" spans="2:5">
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
+      <c r="B175" s="9"/>
+      <c r="C175" s="9"/>
+      <c r="D175" s="9"/>
+      <c r="E175" s="9"/>
     </row>
     <row r="176" ht="27" spans="2:5">
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
+      <c r="B176" s="9"/>
+      <c r="C176" s="9"/>
+      <c r="D176" s="9"/>
+      <c r="E176" s="9"/>
     </row>
     <row r="177" ht="27" spans="2:5">
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
     </row>
     <row r="178" ht="27" spans="2:5">
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
     </row>
     <row r="179" ht="27" spans="2:5">
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
     </row>
     <row r="180" ht="27" spans="2:5">
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
     </row>
     <row r="181" ht="27" spans="2:5">
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
     </row>
     <row r="182" ht="27" spans="2:5">
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
     </row>
     <row r="183" ht="27" spans="2:5">
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
     </row>
     <row r="184" ht="27" spans="2:5">
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
     </row>
     <row r="185" ht="27" spans="2:5">
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
     </row>
     <row r="186" ht="27" spans="2:5">
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
     </row>
     <row r="187" ht="27" spans="2:5">
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
     </row>
     <row r="188" ht="27" spans="2:5">
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
     </row>
     <row r="189" ht="27" spans="2:5">
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
     </row>
     <row r="190" ht="27" spans="2:5">
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
     </row>
     <row r="191" ht="27" spans="2:5">
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
     </row>
     <row r="192" ht="27" spans="2:5">
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
     </row>
     <row r="193" ht="27" spans="2:5">
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
     </row>
     <row r="194" ht="27" spans="2:5">
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
     </row>
     <row r="195" ht="27" spans="2:5">
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
     </row>
     <row r="196" ht="27" spans="2:5">
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
     </row>
     <row r="197" ht="27" spans="2:5">
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
     </row>
     <row r="198" ht="27" spans="2:5">
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
     </row>
     <row r="199" ht="27" spans="2:5">
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
     </row>
     <row r="200" ht="27" spans="2:5">
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
     </row>
     <row r="201" ht="27" spans="2:5">
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
     </row>
     <row r="202" ht="27" spans="2:5">
-      <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
     </row>
     <row r="203" ht="27" spans="2:5">
-      <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
     </row>
     <row r="204" ht="27" spans="2:5">
-      <c r="B204" s="8"/>
-      <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
-      <c r="E204" s="8"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
     </row>
     <row r="205" ht="27" spans="2:5">
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
-      <c r="D205" s="8"/>
-      <c r="E205" s="8"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
     </row>
     <row r="206" ht="27" spans="2:5">
-      <c r="B206" s="8"/>
-      <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
     </row>
     <row r="207" ht="27" spans="2:5">
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="8"/>
-      <c r="E207" s="8"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
     </row>
     <row r="208" ht="27" spans="2:5">
-      <c r="B208" s="8"/>
-      <c r="C208" s="8"/>
-      <c r="D208" s="8"/>
-      <c r="E208" s="8"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
     </row>
     <row r="209" ht="27" spans="2:5">
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
-      <c r="D209" s="8"/>
-      <c r="E209" s="8"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
     </row>
     <row r="210" ht="27" spans="2:5">
-      <c r="B210" s="8"/>
-      <c r="C210" s="8"/>
-      <c r="D210" s="8"/>
-      <c r="E210" s="8"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
     </row>
     <row r="211" ht="27" spans="2:5">
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
-      <c r="D211" s="8"/>
-      <c r="E211" s="8"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="9"/>
+      <c r="D211" s="9"/>
+      <c r="E211" s="9"/>
     </row>
     <row r="212" ht="27" spans="2:5">
-      <c r="B212" s="8"/>
-      <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
-      <c r="E212" s="8"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
     </row>
     <row r="213" ht="27" spans="2:5">
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
     </row>
     <row r="214" ht="27" spans="2:5">
-      <c r="B214" s="8"/>
-      <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
     </row>
     <row r="215" ht="27" spans="2:5">
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="8"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
     </row>
     <row r="216" ht="27" spans="2:5">
-      <c r="B216" s="8"/>
-      <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="8"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
     </row>
     <row r="217" ht="27" spans="2:5">
-      <c r="B217" s="8"/>
-      <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
-      <c r="E217" s="8"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
     </row>
     <row r="218" ht="27" spans="2:5">
-      <c r="B218" s="8"/>
-      <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
-      <c r="E218" s="8"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
     </row>
     <row r="219" ht="27" spans="2:5">
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
-      <c r="E219" s="8"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
+      <c r="E219" s="9"/>
     </row>
     <row r="220" ht="27" spans="2:5">
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
-      <c r="E220" s="8"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
+      <c r="E220" s="9"/>
     </row>
     <row r="221" ht="27" spans="2:5">
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="8"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
     </row>
     <row r="222" ht="27" spans="2:5">
-      <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
     </row>
     <row r="223" ht="27" spans="2:5">
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
-      <c r="E223" s="8"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
+      <c r="E223" s="9"/>
     </row>
     <row r="224" ht="27" spans="2:5">
-      <c r="B224" s="8"/>
-      <c r="C224" s="8"/>
-      <c r="D224" s="8"/>
-      <c r="E224" s="8"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
+      <c r="D224" s="9"/>
+      <c r="E224" s="9"/>
     </row>
     <row r="225" ht="27" spans="2:5">
-      <c r="B225" s="8"/>
-      <c r="C225" s="8"/>
-      <c r="D225" s="8"/>
-      <c r="E225" s="8"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="9"/>
+      <c r="D225" s="9"/>
+      <c r="E225" s="9"/>
     </row>
     <row r="226" ht="27" spans="2:5">
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
-      <c r="E226" s="8"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="9"/>
+      <c r="D226" s="9"/>
+      <c r="E226" s="9"/>
     </row>
     <row r="227" ht="27" spans="2:5">
-      <c r="B227" s="8"/>
-      <c r="C227" s="8"/>
-      <c r="D227" s="8"/>
-      <c r="E227" s="8"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="9"/>
+      <c r="E227" s="9"/>
     </row>
     <row r="228" ht="27" spans="2:5">
-      <c r="B228" s="8"/>
-      <c r="C228" s="8"/>
-      <c r="D228" s="8"/>
-      <c r="E228" s="8"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
+      <c r="E228" s="9"/>
     </row>
     <row r="229" ht="27" spans="2:5">
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
-      <c r="D229" s="8"/>
-      <c r="E229" s="8"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="9"/>
+      <c r="D229" s="9"/>
+      <c r="E229" s="9"/>
     </row>
     <row r="230" ht="27" spans="2:5">
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="8"/>
-      <c r="E230" s="8"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="9"/>
+      <c r="D230" s="9"/>
+      <c r="E230" s="9"/>
     </row>
     <row r="231" ht="27" spans="2:5">
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="8"/>
-      <c r="E231" s="8"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="9"/>
+      <c r="D231" s="9"/>
+      <c r="E231" s="9"/>
     </row>
     <row r="232" ht="27" spans="2:5">
-      <c r="B232" s="8"/>
-      <c r="C232" s="8"/>
-      <c r="D232" s="8"/>
-      <c r="E232" s="8"/>
+      <c r="B232" s="9"/>
+      <c r="C232" s="9"/>
+      <c r="D232" s="9"/>
+      <c r="E232" s="9"/>
     </row>
     <row r="233" ht="27" spans="2:5">
-      <c r="B233" s="8"/>
-      <c r="C233" s="8"/>
-      <c r="D233" s="8"/>
-      <c r="E233" s="8"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
+      <c r="D233" s="9"/>
+      <c r="E233" s="9"/>
     </row>
     <row r="234" ht="27" spans="2:5">
-      <c r="B234" s="8"/>
-      <c r="C234" s="8"/>
-      <c r="D234" s="8"/>
-      <c r="E234" s="8"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="9"/>
+      <c r="D234" s="9"/>
+      <c r="E234" s="9"/>
     </row>
     <row r="235" ht="27" spans="2:5">
-      <c r="B235" s="8"/>
-      <c r="C235" s="8"/>
-      <c r="D235" s="8"/>
-      <c r="E235" s="8"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="9"/>
+      <c r="D235" s="9"/>
+      <c r="E235" s="9"/>
     </row>
     <row r="236" ht="27" spans="2:5">
-      <c r="B236" s="8"/>
-      <c r="C236" s="8"/>
-      <c r="D236" s="8"/>
-      <c r="E236" s="8"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="9"/>
+      <c r="D236" s="9"/>
+      <c r="E236" s="9"/>
     </row>
     <row r="237" ht="27" spans="2:5">
-      <c r="B237" s="8"/>
-      <c r="C237" s="8"/>
-      <c r="D237" s="8"/>
-      <c r="E237" s="8"/>
+      <c r="B237" s="9"/>
+      <c r="C237" s="9"/>
+      <c r="D237" s="9"/>
+      <c r="E237" s="9"/>
     </row>
     <row r="238" ht="27" spans="2:5">
-      <c r="B238" s="8"/>
-      <c r="C238" s="8"/>
-      <c r="D238" s="8"/>
-      <c r="E238" s="8"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="9"/>
+      <c r="D238" s="9"/>
+      <c r="E238" s="9"/>
     </row>
     <row r="239" ht="27" spans="2:5">
-      <c r="B239" s="8"/>
-      <c r="C239" s="8"/>
-      <c r="D239" s="8"/>
-      <c r="E239" s="8"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="9"/>
+      <c r="D239" s="9"/>
+      <c r="E239" s="9"/>
     </row>
     <row r="240" ht="27" spans="2:5">
-      <c r="B240" s="8"/>
-      <c r="C240" s="8"/>
-      <c r="D240" s="8"/>
-      <c r="E240" s="8"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="9"/>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
     </row>
     <row r="241" ht="27" spans="2:5">
-      <c r="B241" s="8"/>
-      <c r="C241" s="8"/>
-      <c r="D241" s="8"/>
-      <c r="E241" s="8"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="9"/>
+      <c r="D241" s="9"/>
+      <c r="E241" s="9"/>
     </row>
     <row r="242" ht="27" spans="2:5">
-      <c r="B242" s="8"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="8"/>
+      <c r="B242" s="9"/>
+      <c r="C242" s="9"/>
+      <c r="D242" s="9"/>
+      <c r="E242" s="9"/>
     </row>
     <row r="243" ht="27" spans="2:5">
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="8"/>
-      <c r="E243" s="8"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="9"/>
+      <c r="D243" s="9"/>
+      <c r="E243" s="9"/>
     </row>
     <row r="244" ht="27" spans="2:5">
-      <c r="B244" s="8"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="8"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="9"/>
+      <c r="D244" s="9"/>
+      <c r="E244" s="9"/>
     </row>
     <row r="245" ht="27" spans="2:5">
-      <c r="B245" s="8"/>
-      <c r="C245" s="8"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="8"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="9"/>
+      <c r="D245" s="9"/>
+      <c r="E245" s="9"/>
     </row>
     <row r="246" ht="27" spans="2:5">
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
-      <c r="D246" s="8"/>
-      <c r="E246" s="8"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="9"/>
+      <c r="D246" s="9"/>
+      <c r="E246" s="9"/>
     </row>
     <row r="247" ht="27" spans="2:5">
-      <c r="B247" s="8"/>
-      <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="8"/>
+      <c r="B247" s="9"/>
+      <c r="C247" s="9"/>
+      <c r="D247" s="9"/>
+      <c r="E247" s="9"/>
     </row>
     <row r="248" ht="27" spans="2:5">
-      <c r="B248" s="8"/>
-      <c r="C248" s="8"/>
-      <c r="D248" s="8"/>
-      <c r="E248" s="8"/>
+      <c r="B248" s="9"/>
+      <c r="C248" s="9"/>
+      <c r="D248" s="9"/>
+      <c r="E248" s="9"/>
     </row>
     <row r="249" ht="27" spans="2:5">
-      <c r="B249" s="8"/>
-      <c r="C249" s="8"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="8"/>
+      <c r="B249" s="9"/>
+      <c r="C249" s="9"/>
+      <c r="D249" s="9"/>
+      <c r="E249" s="9"/>
     </row>
     <row r="250" ht="27" spans="2:5">
-      <c r="B250" s="8"/>
-      <c r="C250" s="8"/>
-      <c r="D250" s="8"/>
-      <c r="E250" s="8"/>
+      <c r="B250" s="9"/>
+      <c r="C250" s="9"/>
+      <c r="D250" s="9"/>
+      <c r="E250" s="9"/>
     </row>
     <row r="251" ht="27" spans="2:5">
-      <c r="B251" s="8"/>
-      <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="8"/>
+      <c r="B251" s="9"/>
+      <c r="C251" s="9"/>
+      <c r="D251" s="9"/>
+      <c r="E251" s="9"/>
     </row>
     <row r="252" ht="27" spans="2:5">
-      <c r="B252" s="8"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="8"/>
+      <c r="B252" s="9"/>
+      <c r="C252" s="9"/>
+      <c r="D252" s="9"/>
+      <c r="E252" s="9"/>
     </row>
     <row r="253" ht="27" spans="2:5">
-      <c r="B253" s="8"/>
-      <c r="C253" s="8"/>
-      <c r="D253" s="8"/>
-      <c r="E253" s="8"/>
+      <c r="B253" s="9"/>
+      <c r="C253" s="9"/>
+      <c r="D253" s="9"/>
+      <c r="E253" s="9"/>
     </row>
     <row r="254" ht="27" spans="2:5">
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
-      <c r="D254" s="8"/>
-      <c r="E254" s="8"/>
+      <c r="B254" s="9"/>
+      <c r="C254" s="9"/>
+      <c r="D254" s="9"/>
+      <c r="E254" s="9"/>
     </row>
     <row r="255" ht="27" spans="2:5">
-      <c r="B255" s="8"/>
-      <c r="C255" s="8"/>
-      <c r="D255" s="8"/>
-      <c r="E255" s="8"/>
+      <c r="B255" s="9"/>
+      <c r="C255" s="9"/>
+      <c r="D255" s="9"/>
+      <c r="E255" s="9"/>
     </row>
     <row r="256" ht="27" spans="2:5">
-      <c r="B256" s="8"/>
-      <c r="C256" s="8"/>
-      <c r="D256" s="8"/>
-      <c r="E256" s="8"/>
+      <c r="B256" s="9"/>
+      <c r="C256" s="9"/>
+      <c r="D256" s="9"/>
+      <c r="E256" s="9"/>
     </row>
     <row r="257" ht="27" spans="2:5">
-      <c r="B257" s="8"/>
-      <c r="C257" s="8"/>
-      <c r="D257" s="8"/>
-      <c r="E257" s="8"/>
+      <c r="B257" s="9"/>
+      <c r="C257" s="9"/>
+      <c r="D257" s="9"/>
+      <c r="E257" s="9"/>
     </row>
     <row r="323" ht="27" spans="2:5">
-      <c r="B323" s="7"/>
-      <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="10"/>
+      <c r="B323" s="8"/>
+      <c r="C323" s="10"/>
+      <c r="D323" s="10"/>
+      <c r="E323" s="11"/>
     </row>
     <row r="324" spans="2:5">
       <c r="B324" s="6"/>
-      <c r="C324" s="11"/>
-      <c r="D324" s="11"/>
-      <c r="E324" s="11"/>
+      <c r="C324" s="12"/>
+      <c r="D324" s="12"/>
+      <c r="E324" s="12"/>
     </row>
     <row r="325" spans="2:5">
       <c r="B325" s="6"/>
-      <c r="C325" s="11"/>
-      <c r="D325" s="11"/>
-      <c r="E325" s="11"/>
+      <c r="C325" s="12"/>
+      <c r="D325" s="12"/>
+      <c r="E325" s="12"/>
     </row>
     <row r="326" spans="2:5">
       <c r="B326" s="6"/>
-      <c r="C326" s="11"/>
-      <c r="D326" s="11"/>
-      <c r="E326" s="11"/>
+      <c r="C326" s="12"/>
+      <c r="D326" s="12"/>
+      <c r="E326" s="12"/>
     </row>
     <row r="327" spans="2:5">
       <c r="B327" s="6"/>
-      <c r="C327" s="11"/>
-      <c r="D327" s="11"/>
-      <c r="E327" s="11"/>
+      <c r="C327" s="12"/>
+      <c r="D327" s="12"/>
+      <c r="E327" s="12"/>
     </row>
     <row r="328" spans="2:5">
       <c r="B328" s="6"/>
-      <c r="C328" s="11"/>
-      <c r="D328" s="11"/>
-      <c r="E328" s="11"/>
+      <c r="C328" s="12"/>
+      <c r="D328" s="12"/>
+      <c r="E328" s="12"/>
     </row>
     <row r="329" spans="2:5">
       <c r="B329" s="6"/>
-      <c r="C329" s="11"/>
-      <c r="D329" s="11"/>
-      <c r="E329" s="11"/>
+      <c r="C329" s="12"/>
+      <c r="D329" s="12"/>
+      <c r="E329" s="12"/>
     </row>
     <row r="330" spans="2:5">
       <c r="B330" s="6"/>
-      <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
-      <c r="E330" s="11"/>
+      <c r="C330" s="12"/>
+      <c r="D330" s="12"/>
+      <c r="E330" s="12"/>
     </row>
     <row r="331" spans="2:5">
       <c r="B331" s="6"/>
-      <c r="C331" s="11"/>
-      <c r="D331" s="11"/>
-      <c r="E331" s="11"/>
+      <c r="C331" s="12"/>
+      <c r="D331" s="12"/>
+      <c r="E331" s="12"/>
     </row>
     <row r="332" spans="2:5">
       <c r="B332" s="6"/>
-      <c r="C332" s="11"/>
-      <c r="D332" s="11"/>
-      <c r="E332" s="11"/>
+      <c r="C332" s="12"/>
+      <c r="D332" s="12"/>
+      <c r="E332" s="12"/>
     </row>
     <row r="333" spans="2:5">
       <c r="B333" s="6"/>
@@ -19273,7 +19277,7 @@
       <c r="E1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1LN74zNAw1oTFwPgk67G/jfQyMmdd3sLFOS+F2ULzBvPvi6Qc0vyjAT6ON2pJK6Kpec/OwqRP54Ykx8AlIHmiQ==" saltValue="f6Jlv0x8ksU/QuoNbufrqg==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0/A1qRoS9m5CnneSgY5Gac/tXBt18yX2AnQYsHDr0Qc5TxUR9TsRmn2x5JXnRn84Y37H/s4r5thyQ43xYbMBOQ==" saltValue="nHF6n4H63SX/YedW2qFhXQ==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="B2:C2">
     <cfRule type="expression" dxfId="0" priority="45">
       <formula>"ISEVEN(ROW())"</formula>
@@ -19354,35 +19358,35 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="36.1428571428571" hidden="1" customWidth="1"/>
-    <col min="2" max="7" width="30.7142857142857" customWidth="1"/>
+    <col min="2" max="7" width="40.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="2" ht="27" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -19393,7 +19397,7 @@
     </row>
     <row r="3" ht="27" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -25996,7 +26000,7 @@
       <c r="G1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="R+FN/++3z5qDIvUfagayxkjkTC6GMLfhnaJ6lcbgasOkTr0OXE+/KM6oe2cpEoDyEPuVAlgRuReLAf3xGwAQ4w==" saltValue="vSoIIGAKUObJf+na5VGmPw==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ujl0VIUQs127FA1O8EVrXEwiHMuZPh4MQcaQ2D1gM4XkLI2hw0Lj92r9iITBO+wlEF07+E4Uw+Ukk8nQZUJgDw==" saltValue="hOZcwFl4b6fJ20Ok4plY3w==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="F12">
     <cfRule type="expression" dxfId="0" priority="45">
       <formula>"ISEVEN(ROW())"</formula>
@@ -26127,10 +26131,10 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>38</v>
@@ -31244,7 +31248,7 @@
       <c r="E1000" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VYn2e6t5QafVhmux2FmZzO4rG+0cQaXbz/YXAYrXlHE53uXa3GOGlCEkFsLtTlrXit8uQOqKoZ5L+0QdwE6kbw==" saltValue="WM0O85bOT9D/RcBsu1DdcA==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wh6wa9azYDvZwqHApHuK5E255voeh7MtPsD9x8BXUUk7ZXbfrysMKosDatV8tRXSlnWLNJLgB++0GYeeKm2XGA==" saltValue="/zij2HqYVuZB+8wqI8einQ==" spinCount="100000" sheet="1" objects="1"/>
   <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="0" priority="36">
       <formula>"ISEVEN(ROW())"</formula>
@@ -31353,10 +31357,10 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>38</v>
